--- a/public/file/Trax Book Try And Buy Shipment Template.xlsx
+++ b/public/file/Trax Book Try And Buy Shipment Template.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -54,9 +54,6 @@
   </si>
   <si>
     <t>Show Information on Air Waybill</t>
-  </si>
-  <si>
-    <t>Collection Amount</t>
   </si>
   <si>
     <t>Consignee Phone Number 2 (03000000000)</t>
@@ -502,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AP1"/>
+  <dimension ref="A1:AO1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -543,12 +540,11 @@
     <col min="37" max="37" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="17.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="15" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -556,7 +552,7 @@
         <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -565,10 +561,10 @@
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
@@ -577,79 +573,79 @@
         <v>3</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="AI1" s="1" t="s">
         <v>4</v>
@@ -661,19 +657,16 @@
         <v>7</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Try And Buy Shipment Template.xlsx
+++ b/public/file/Trax Book Try And Buy Shipment Template.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23231"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377DB565-D66F-4FEE-95BB-4EF88C7C9805}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="12696"/>
+    <workbookView xWindow="204" yWindow="2376" windowWidth="17280" windowHeight="8976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -147,12 +148,15 @@
   </si>
   <si>
     <t>Same Day Timing ID</t>
+  </si>
+  <si>
+    <t>Order Date (YYYY-MM-DD)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -498,8 +502,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AO1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AP1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -510,41 +514,42 @@
     <col min="6" max="7" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.88671875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="24" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.21875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="24" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="26.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="24" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="26.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="23.88671875" style="1" customWidth="1"/>
-    <col min="28" max="28" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="24" style="1" customWidth="1"/>
-    <col min="30" max="30" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="26.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="24" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.88671875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26.21875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="26.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="26.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="23.88671875" style="1" customWidth="1"/>
+    <col min="29" max="29" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="24" style="1" customWidth="1"/>
+    <col min="31" max="31" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="26.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -573,99 +578,102 @@
         <v>3</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>13</v>
       </c>
     </row>

--- a/public/file/Trax Book Try And Buy Shipment Template.xlsx
+++ b/public/file/Trax Book Try And Buy Shipment Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377DB565-D66F-4FEE-95BB-4EF88C7C9805}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9F86A7-7AC2-4CC9-B8F6-3BF6B6428893}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="204" yWindow="2376" windowWidth="17280" windowHeight="8976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -151,6 +151,21 @@
   </si>
   <si>
     <t>Order Date (YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 1</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 2</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 3</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 4</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 5</t>
   </si>
 </sst>
 </file>
@@ -503,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AP1"/>
+  <dimension ref="A1:AU1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -547,9 +562,10 @@
     <col min="40" max="40" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="18" style="1" bestFit="1" customWidth="1"/>
     <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="47" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -675,6 +691,21 @@
       </c>
       <c r="AP1" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Try And Buy Shipment Template.xlsx
+++ b/public/file/Trax Book Try And Buy Shipment Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9F86A7-7AC2-4CC9-B8F6-3BF6B6428893}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F6817E-68B5-49E7-A3C8-8A5C2AA20826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -166,6 +166,9 @@
   </si>
   <si>
     <t>Shipper Reference Number 5</t>
+  </si>
+  <si>
+    <t>Open Shipment</t>
   </si>
 </sst>
 </file>
@@ -518,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AU1"/>
+  <dimension ref="A1:AV1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -565,7 +568,7 @@
     <col min="43" max="47" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -706,6 +709,9 @@
       </c>
       <c r="AU1" t="s">
         <v>46</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Try And Buy Shipment Template.xlsx
+++ b/public/file/Trax Book Try And Buy Shipment Template.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F6817E-68B5-49E7-A3C8-8A5C2AA20826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="3396" windowWidth="17280" windowHeight="8964"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -169,12 +168,18 @@
   </si>
   <si>
     <t>Open Shipment</t>
+  </si>
+  <si>
+    <t>Consignee Address Latitude</t>
+  </si>
+  <si>
+    <t>Consignee Address Longitude</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -520,8 +525,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AV1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AX1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -531,44 +536,45 @@
     <col min="5" max="5" width="16.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="26.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.88671875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="24" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="26.21875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="26.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="24" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="26.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="23.88671875" style="1" customWidth="1"/>
-    <col min="29" max="29" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="24" style="1" customWidth="1"/>
-    <col min="31" max="31" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="26.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="24" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="47" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="21.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.88671875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.21875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="26.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="23.88671875" style="1" customWidth="1"/>
+    <col min="31" max="31" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="24" style="1" customWidth="1"/>
+    <col min="33" max="33" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="26.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="49" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -594,123 +600,129 @@
         <v>2</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AT1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>47</v>
       </c>
     </row>

--- a/public/file/Trax Book Try And Buy Shipment Template.xlsx
+++ b/public/file/Trax Book Try And Buy Shipment Template.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -174,6 +174,12 @@
   </si>
   <si>
     <t>Consignee Address Longitude</t>
+  </si>
+  <si>
+    <t>Retail Pickup Store ID</t>
+  </si>
+  <si>
+    <t>Retail Deliver Store ID</t>
   </si>
 </sst>
 </file>
@@ -526,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AX1"/>
+  <dimension ref="A1:AZ1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -572,9 +578,11 @@
     <col min="43" max="43" width="18" style="1" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="45" max="49" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -724,6 +732,12 @@
       </c>
       <c r="AX1" t="s">
         <v>47</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
